--- a/data/trans_bre/IP16B01-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16B01-Estudios-trans_bre.xlsx
@@ -639,12 +639,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-28,85; 15,82</t>
+          <t>-30,09; 19,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-34,58; 31,28</t>
+          <t>-31,95; 25,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,86; 20,73</t>
+          <t>-32,28; 23,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,33; 40,84</t>
+          <t>-34,31; 39,13</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,24</t>
+          <t>0,0; 4,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,62; -2,67</t>
+          <t>-20,71; -3,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 2,95</t>
+          <t>-23,27; 1,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,64; -2,96</t>
+          <t>-21,36; -3,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,9; 3,25</t>
+          <t>-25,45; 0,92</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,39</t>
+          <t>0,0; 14,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-28,67; 4,9</t>
+          <t>-27,49; 5,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 22,39</t>
+          <t>-14,91; 26,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-30,45; 5,05</t>
+          <t>-28,85; 6,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 33,23</t>
+          <t>-15,88; 39,38</t>
         </is>
       </c>
     </row>
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,16; -3,56</t>
+          <t>-18,93; -3,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 3,5</t>
+          <t>-16,11; 2,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,3; -3,97</t>
+          <t>-20,29; -4,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,48; 4,18</t>
+          <t>-17,81; 3,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16B01-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16B01-Estudios-trans_bre.xlsx
@@ -639,12 +639,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-30,09; 19,1</t>
+          <t>-31,66; 15,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-31,95; 25,86</t>
+          <t>-33,16; 26,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-32,28; 23,7</t>
+          <t>-34,62; 19,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,31; 39,13</t>
+          <t>-35,26; 40,0</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,4</t>
+          <t>0,0; 4,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,71; -3,3</t>
+          <t>-20,31; -3,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-23,27; 1,04</t>
+          <t>-23,54; 1,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,36; -3,66</t>
+          <t>-21,2; -3,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-25,45; 0,92</t>
+          <t>-25,42; 1,67</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,31</t>
+          <t>0,0; 14,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-27,49; 5,63</t>
+          <t>-29,4; 6,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 26,31</t>
+          <t>-15,47; 24,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,85; 6,72</t>
+          <t>-31,28; 6,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 39,38</t>
+          <t>-16,01; 35,01</t>
         </is>
       </c>
     </row>
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,93; -3,9</t>
+          <t>-19,32; -3,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 2,85</t>
+          <t>-16,29; 2,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,29; -4,37</t>
+          <t>-20,1; -4,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 3,37</t>
+          <t>-18,19; 3,15</t>
         </is>
       </c>
     </row>
